--- a/outputs/portfolio_combined/performance_stats.xlsx
+++ b/outputs/portfolio_combined/performance_stats.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003897583779881881</v>
+        <v>0.01408323814220355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004345242433672408</v>
+        <v>0.01759693080070231</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8969772893863173</v>
+        <v>0.800323550834301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04843548518128937</v>
+        <v>0.1845704332844647</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005279709083752996</v>
+        <v>-0.02662379463429686</v>
       </c>
     </row>
     <row r="5">
